--- a/data/trans_dic/P55$auxiliar-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P55$auxiliar-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,26</t>
+          <t>0,0; 29,08</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,32</t>
+          <t>0,0; 68,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,13</t>
+          <t>0,0; 23,29</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 8,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,48</t>
+          <t>0,0; 33,11</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,0; 18,1</t>
+          <t>2,03; 16,19</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,95</t>
+          <t>0,0; 63,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,86</t>
+          <t>0,0; 20,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,61</t>
+          <t>0,0; 68,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,11; 41,2</t>
+          <t>8,43; 41,6</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,02</t>
+          <t>0,0; 36,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,52</t>
+          <t>0,0; 35,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,87; 24,42</t>
+          <t>5,71; 24,42</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,87</t>
+          <t>0,0; 22,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,24; 36,09</t>
+          <t>10,38; 35,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,14; 51,61</t>
+          <t>11,3; 52,55</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>12,98; 43,19</t>
+          <t>13,7; 42,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 6,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,21; 29,85</t>
+          <t>5,02; 28,61</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,1; 33,2</t>
+          <t>15,42; 34,26</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,97</t>
+          <t>0,0; 5,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,54; 12,92</t>
+          <t>1,5; 12,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 18,56</t>
+          <t>2,02; 18,74</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,09; 32,45</t>
+          <t>16,61; 33,43</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,8</t>
+          <t>0,0; 24,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,89</t>
+          <t>0,0; 21,81</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,42</t>
+          <t>0,0; 24,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,21; 32,95</t>
+          <t>14,14; 31,79</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,15</t>
+          <t>0,0; 7,66</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 10,91</t>
+          <t>1,23; 11,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,21; 15,58</t>
+          <t>2,3; 15,5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,78; 30,46</t>
+          <t>17,74; 30,22</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,0; 30,14</t>
+          <t>6,03; 33,43</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,66; 15,17</t>
+          <t>1,62; 14,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,24; 28,76</t>
+          <t>7,48; 28,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,8; 25,58</t>
+          <t>2,98; 25,09</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,64; 34,69</t>
+          <t>14,63; 34,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,79</t>
+          <t>0,0; 12,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,52; 35,63</t>
+          <t>22,74; 35,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 18,08</t>
+          <t>2,0; 17,39</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13,92; 29,04</t>
+          <t>14,89; 29,46</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,94; 10,19</t>
+          <t>0,99; 8,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,37; 31,38</t>
+          <t>20,24; 31,61</t>
         </is>
       </c>
     </row>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,78; 6,91</t>
+          <t>0,81; 7,66</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,02; 25,16</t>
+          <t>12,07; 25,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,39; 14,4</t>
+          <t>4,21; 14,39</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,38; 29,53</t>
+          <t>19,44; 29,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,77; 7,19</t>
+          <t>0,78; 8,21</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,02; 25,16</t>
+          <t>12,07; 25,39</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,39; 14,4</t>
+          <t>4,21; 14,39</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,59; 28,67</t>
+          <t>18,88; 28,95</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,64</t>
+          <t>0,0; 3,59</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,28; 14,05</t>
+          <t>4,21; 13,99</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,08; 9,95</t>
+          <t>2,01; 9,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,83; 23,81</t>
+          <t>13,39; 23,37</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,87; 7,42</t>
+          <t>1,91; 7,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,2; 23,75</t>
+          <t>13,87; 23,44</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,98; 11,6</t>
+          <t>3,65; 10,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,22; 27,97</t>
+          <t>21,05; 27,62</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,62; 5,47</t>
+          <t>1,51; 5,32</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,63; 19,08</t>
+          <t>11,61; 18,49</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,68; 9,07</t>
+          <t>3,98; 8,77</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,83; 25,19</t>
+          <t>19,68; 25,1</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1901</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1953</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1634</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4110</t>
+          <t>0; 3488</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 1803</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1448</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4290</t>
+          <t>0; 5503</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2789</t>
+          <t>0; 3227</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1944</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 1991</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5950</t>
+          <t>0; 4990</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>518; 4680</t>
+          <t>524; 4186</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1844</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5892</t>
+          <t>0; 6003</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1560</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3468</t>
+          <t>0; 3608</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1636</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1828</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4739</t>
+          <t>0; 4628</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1113; 5652</t>
+          <t>1156; 5706</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1911</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 6781</t>
+          <t>0; 6743</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 6553</t>
+          <t>0; 6192</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1829; 7612</t>
+          <t>1779; 7614</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1630</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5587</t>
+          <t>0; 5394</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1565</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2170; 7647</t>
+          <t>2199; 7547</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1726</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2117; 9806</t>
+          <t>2147; 9984</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 2199</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2749; 9147</t>
+          <t>2902; 8944</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1731</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2263; 12965</t>
+          <t>2182; 12429</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 1895</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6396; 14064</t>
+          <t>6531; 14515</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4217</t>
+          <t>0; 4206</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1045; 8761</t>
+          <t>1017; 8781</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>806; 7400</t>
+          <t>804; 7470</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11590; 23373</t>
+          <t>11961; 24083</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5575</t>
+          <t>0; 5702</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5810</t>
+          <t>0; 4545</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 9001</t>
+          <t>0; 8195</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5512; 12779</t>
+          <t>5485; 12329</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 6725</t>
+          <t>0; 7203</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1066; 9666</t>
+          <t>1093; 9942</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1608; 11326</t>
+          <t>1672; 11265</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19704; 33759</t>
+          <t>19663; 33491</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1694</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2163; 10860</t>
+          <t>2174; 12045</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>784; 7180</t>
+          <t>767; 6755</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2176; 8648</t>
+          <t>2248; 8507</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1021; 9316</t>
+          <t>1084; 9137</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12234; 28983</t>
+          <t>12229; 28599</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 5191</t>
+          <t>0; 6391</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>20993; 33206</t>
+          <t>21197; 32886</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>956; 9493</t>
+          <t>1051; 9128</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16649; 34733</t>
+          <t>17804; 35232</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>939; 10226</t>
+          <t>995; 8890</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>25104; 38687</t>
+          <t>24955; 38966</t>
         </is>
       </c>
     </row>
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 705</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 778</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1125; 9953</t>
+          <t>1163; 11034</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17195; 36008</t>
+          <t>17276; 36336</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6472; 21209</t>
+          <t>6205; 21194</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>27319; 41636</t>
+          <t>27411; 41633</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1113; 10419</t>
+          <t>1125; 11904</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17195; 36008</t>
+          <t>17276; 36336</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6472; 21209</t>
+          <t>6205; 21194</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>26618; 41036</t>
+          <t>27019; 41439</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4607</t>
+          <t>0; 4547</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6250; 20530</t>
+          <t>6158; 20445</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2529; 12082</t>
+          <t>2442; 11524</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21414; 36874</t>
+          <t>20744; 36199</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4324; 17142</t>
+          <t>4420; 17722</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>39561; 66152</t>
+          <t>38623; 65290</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10508; 30651</t>
+          <t>9646; 28254</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>68266; 89991</t>
+          <t>67735; 88852</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5776; 19551</t>
+          <t>5392; 19014</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49403; 81041</t>
+          <t>49311; 78540</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>14173; 34972</t>
+          <t>15352; 33833</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>94528; 120078</t>
+          <t>93777; 119614</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$auxiliar-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P55$auxiliar-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,08</t>
+          <t>0,0; 30,64</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,4</t>
+          <t>0,0; 68,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,29</t>
+          <t>0,0; 21,08</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,11</t>
+          <t>0,0; 40,87</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 16,19</t>
+          <t>1,85; 17,12</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,13</t>
+          <t>0,0; 62,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,67</t>
+          <t>0,0; 21,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -887,12 +887,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,96</t>
+          <t>0,0; 70,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,43; 41,6</t>
+          <t>10,01; 41,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,81</t>
+          <t>0,0; 33,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,46</t>
+          <t>0,0; 28,88</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,71; 24,42</t>
+          <t>5,32; 24,47</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>27,28%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>23,46%</t>
+          <t>24,95%</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,07</t>
+          <t>0,0; 18,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,38; 35,62</t>
+          <t>11,22; 38,88</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,3; 52,55</t>
+          <t>11,16; 52,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,7; 42,23</t>
+          <t>14,28; 44,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,02; 28,61</t>
+          <t>6,79; 29,32</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,42; 34,26</t>
+          <t>16,07; 35,99</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23,92%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>23,88%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,96</t>
+          <t>0,0; 4,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 12,95</t>
+          <t>1,51; 13,05</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,02; 18,74</t>
+          <t>2,08; 18,85</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16,61; 33,43</t>
+          <t>16,83; 32,92</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,34</t>
+          <t>0,0; 24,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,81</t>
+          <t>0,0; 23,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,96</t>
+          <t>0,0; 20,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14,14; 31,79</t>
+          <t>14,69; 33,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,66</t>
+          <t>0,0; 7,55</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,23; 11,22</t>
+          <t>1,24; 11,22</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,3; 15,5</t>
+          <t>2,24; 16,09</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>17,74; 30,22</t>
+          <t>18,18; 29,85</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>24,7%</t>
         </is>
       </c>
     </row>
@@ -1282,64 +1282,64 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>6,03; 33,43</t>
+          <t>6,0; 32,4</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,62; 14,27</t>
+          <t>1,67; 14,62</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,48; 28,29</t>
+          <t>6,91; 26,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,98; 25,09</t>
+          <t>2,84; 25,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,63; 34,23</t>
+          <t>15,23; 33,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,05</t>
+          <t>0,0; 11,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,74; 35,29</t>
+          <t>22,15; 35,3</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 17,39</t>
+          <t>1,92; 17,14</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,89; 29,46</t>
+          <t>13,84; 29,49</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 8,86</t>
+          <t>1,23; 8,86</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>20,24; 31,61</t>
+          <t>19,19; 30,23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,66</t>
+          <t>0,78; 8,51</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,07; 25,39</t>
+          <t>11,52; 24,82</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,21; 14,39</t>
+          <t>4,12; 13,94</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>19,44; 29,53</t>
+          <t>18,57; 28,22</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,78; 8,21</t>
+          <t>0,78; 7,08</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,07; 25,39</t>
+          <t>11,52; 24,82</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,21; 14,39</t>
+          <t>4,12; 13,94</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>18,88; 28,95</t>
+          <t>18,21; 28,66</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>22,44%</t>
+          <t>22,3%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 3,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,21; 13,99</t>
+          <t>4,38; 13,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,01; 9,49</t>
+          <t>2,0; 9,63</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13,39; 23,37</t>
+          <t>14,17; 23,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,67</t>
+          <t>1,99; 7,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,87; 23,44</t>
+          <t>13,97; 23,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,65; 10,7</t>
+          <t>3,76; 10,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>21,05; 27,62</t>
+          <t>20,75; 27,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,51; 5,32</t>
+          <t>1,31; 5,09</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>11,61; 18,49</t>
+          <t>11,57; 18,71</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,98; 8,77</t>
+          <t>3,85; 9,35</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>19,68; 25,1</t>
+          <t>19,65; 25,4</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>669</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1801</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3488</t>
+          <t>0; 3831</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 5503</t>
+          <t>0; 5480</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3227</t>
+          <t>0; 3161</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4990</t>
+          <t>0; 6161</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>524; 4186</t>
+          <t>509; 4708</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2988</t>
+          <t>3519</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4068</t>
+          <t>4602</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6003</t>
+          <t>0; 5953</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3608</t>
+          <t>0; 3967</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4628</t>
+          <t>0; 4724</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1156; 5706</t>
+          <t>1555; 6485</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2180,17 +2180,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 6743</t>
+          <t>0; 6174</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 6192</t>
+          <t>0; 5043</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1779; 7614</t>
+          <t>1826; 8392</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4367</t>
+          <t>5127</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>5574</t>
+          <t>6514</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9941</t>
+          <t>11641</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5394</t>
+          <t>0; 4582</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2199; 7547</t>
+          <t>2558; 8860</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2147; 9984</t>
+          <t>2120; 9892</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2902; 8944</t>
+          <t>3409; 10552</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2182; 12429</t>
+          <t>2950; 12734</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6531; 14515</t>
+          <t>7499; 16793</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>17231</t>
+          <t>18764</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8660</t>
+          <t>9645</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>28408</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4206</t>
+          <t>0; 3378</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1017; 8781</t>
+          <t>1022; 8849</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>804; 7470</t>
+          <t>830; 7514</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>11961; 24083</t>
+          <t>12985; 25393</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 5702</t>
+          <t>0; 5754</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4545</t>
+          <t>0; 4839</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 8195</t>
+          <t>0; 6822</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5485; 12329</t>
+          <t>6147; 13925</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 7203</t>
+          <t>0; 7104</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1093; 9942</t>
+          <t>1095; 9947</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1672; 11265</t>
+          <t>1626; 11695</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19663; 33491</t>
+          <t>21635; 35510</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4732</t>
+          <t>4630</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>26927</t>
+          <t>28370</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>31659</t>
+          <t>33000</t>
         </is>
       </c>
     </row>
@@ -2764,64 +2764,64 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2174; 12045</t>
+          <t>2162; 11675</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>767; 6755</t>
+          <t>788; 6920</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2248; 8507</t>
+          <t>2273; 8875</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1084; 9137</t>
+          <t>1036; 9386</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12229; 28599</t>
+          <t>12722; 28073</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6391</t>
+          <t>0; 6166</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21197; 32886</t>
+          <t>22313; 35556</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1051; 9128</t>
+          <t>1007; 8995</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>17804; 35232</t>
+          <t>16557; 35269</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>995; 8890</t>
+          <t>1234; 8895</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>24955; 38966</t>
+          <t>25636; 40393</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>33673</t>
+          <t>35474</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>33673</t>
+          <t>35474</t>
         </is>
       </c>
     </row>
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1163; 11034</t>
+          <t>1130; 12254</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>17276; 36336</t>
+          <t>16478; 35519</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6205; 21194</t>
+          <t>6066; 20530</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>27411; 41633</t>
+          <t>28240; 42921</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1125; 11904</t>
+          <t>1137; 10257</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>17276; 36336</t>
+          <t>16478; 35519</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6205; 21194</t>
+          <t>6066; 20530</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>27019; 41439</t>
+          <t>28094; 44216</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>28547</t>
+          <t>30736</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>78412</t>
+          <t>84190</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>106959</t>
+          <t>114926</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4547</t>
+          <t>0; 4266</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>6158; 20445</t>
+          <t>6405; 19858</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2442; 11524</t>
+          <t>2430; 11702</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>20744; 36199</t>
+          <t>23566; 39123</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>4420; 17722</t>
+          <t>4599; 17041</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38623; 65290</t>
+          <t>38926; 66635</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9646; 28254</t>
+          <t>9927; 27763</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>67735; 88852</t>
+          <t>72446; 96248</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>5392; 19014</t>
+          <t>4675; 18213</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49311; 78540</t>
+          <t>49160; 79451</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15352; 33833</t>
+          <t>14833; 36057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>93777; 119614</t>
+          <t>101289; 130883</t>
         </is>
       </c>
     </row>
